--- a/tasks_2_3.xlsx
+++ b/tasks_2_3.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="6" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 2" sheetId="1" state="visible" r:id="rId1"/>
@@ -53973,42 +53973,42 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>557</v>
+        <v>816</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>796</v>
+        <v>1055</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>958</v>
+        <v>863</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>236</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1197</v>
+        <v>1102</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>238</v>
@@ -54019,91 +54019,91 @@
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>578</v>
+        <v>270</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>817</v>
+        <v>509</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>796</v>
+        <v>202</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1035</v>
+        <v>441</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>325</v>
+        <v>401</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>243</v>
+        <v>556</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>482</v>
+        <v>795</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
@@ -54111,180 +54111,180 @@
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>699</v>
+        <v>730</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>938</v>
+        <v>969</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>160</v>
+        <v>402</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>399</v>
+        <v>641</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>525</v>
+        <v>703</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>764</v>
+        <v>942</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>36</v>
+        <v>477</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>275</v>
+        <v>716</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>541</v>
+        <v>822</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>780</v>
+        <v>1061</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>171</v>
+        <v>772</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>177</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>410</v>
+        <v>1011</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>655</v>
+        <v>106</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>894</v>
+        <v>345</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>891</v>
+        <v>566</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1130</v>
+        <v>805</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>183</v>
+        <v>120</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>232</v>
@@ -54295,154 +54295,154 @@
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>858</v>
+        <v>390</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1097</v>
+        <v>629</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>183</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>848</v>
+        <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1087</v>
+        <v>234</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>183</v>
+        <v>7</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>205</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>734</v>
+        <v>983</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>169</v>
+        <v>222</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>973</v>
+        <v>1222</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>96</v>
+        <v>562</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>335</v>
+        <v>801</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>564</v>
+        <v>81</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>803</v>
+        <v>320</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>480</v>
+        <v>445</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>54</v>
@@ -54456,91 +54456,91 @@
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>743</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>982</v>
+        <v>274</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>162</v>
+        <v>7</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>575</v>
+        <v>776</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>814</v>
+        <v>1015</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>691</v>
+        <v>509</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>930</v>
+        <v>748</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>461</v>
+        <v>428</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>700</v>
+        <v>667</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -54548,45 +54548,45 @@
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>554</v>
+        <v>455</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>793</v>
+        <v>694</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>889</v>
+        <v>367</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>201</v>
+        <v>90</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1128</v>
+        <v>606</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>183</v>
+        <v>76</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>9</v>
@@ -54594,19 +54594,19 @@
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>207</v>
+        <v>92</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>446</v>
+        <v>331</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>235</v>
@@ -54617,114 +54617,114 @@
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>632</v>
+        <v>579</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>76</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>795</v>
+        <v>898</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1034</v>
+        <v>1137</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>398</v>
+        <v>565</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>637</v>
+        <v>804</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>767</v>
+        <v>346</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>176</v>
+        <v>86</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1006</v>
+        <v>585</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>849</v>
+        <v>777</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1088</v>
+        <v>1016</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>9</v>
@@ -54732,91 +54732,91 @@
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>769</v>
+        <v>316</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1008</v>
+        <v>555</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>643</v>
+        <v>601</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>882</v>
+        <v>840</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
@@ -54824,68 +54824,68 @@
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>930</v>
+        <v>388</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>1169</v>
+        <v>627</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>205</v>
+        <v>76</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>613</v>
+        <v>274</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>852</v>
+        <v>513</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>739</v>
+        <v>167</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>978</v>
+        <v>406</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>9</v>
@@ -54893,45 +54893,45 @@
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>547</v>
+        <v>841</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>786</v>
+        <v>1080</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>726</v>
+        <v>993</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>965</v>
+        <v>1232</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
@@ -54939,22 +54939,22 @@
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>684</v>
+        <v>647</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>923</v>
+        <v>886</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>141</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>9</v>
@@ -54962,19 +54962,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>99</v>
+        <v>819</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>239</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>30</v>
+        <v>187</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>338</v>
+        <v>1058</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>7</v>
+        <v>183</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>241</v>
@@ -54985,19 +54985,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>805</v>
+        <v>485</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>242</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1044</v>
+        <v>724</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>183</v>
+        <v>98</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>244</v>
@@ -55008,22 +55008,22 @@
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>728</v>
+        <v>981</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>967</v>
+        <v>1220</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>15</v>
@@ -55031,42 +55031,42 @@
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>574</v>
+        <v>505</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>813</v>
+        <v>744</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>120</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>407</v>
+        <v>832</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>646</v>
+        <v>1071</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>235</v>
@@ -55077,68 +55077,68 @@
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>503</v>
+        <v>244</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>742</v>
+        <v>483</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>48</v>
+        <v>567</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>287</v>
+        <v>806</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>33</v>
+        <v>876</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>16</v>
+        <v>199</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>272</v>
+        <v>1115</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>7</v>
+        <v>183</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>15</v>
@@ -55146,134 +55146,134 @@
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>780</v>
+        <v>563</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>1019</v>
+        <v>802</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>840</v>
+        <v>687</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>1079</v>
+        <v>926</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>135</v>
+        <v>783</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>374</v>
+        <v>1022</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>28</v>
+        <v>700</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>267</v>
+        <v>939</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>881</v>
+        <v>476</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>1120</v>
+        <v>715</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>183</v>
+        <v>98</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>232</v>
@@ -55284,137 +55284,137 @@
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>231</v>
+        <v>682</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>470</v>
+        <v>921</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>729</v>
+        <v>750</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>773</v>
+        <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1012</v>
+        <v>298</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>162</v>
+        <v>7</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>379</v>
+        <v>475</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>618</v>
+        <v>714</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>289</v>
+        <v>561</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>528</v>
+        <v>800</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>419</v>
+        <v>857</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>658</v>
+        <v>1096</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>9</v>
@@ -55422,88 +55422,88 @@
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>675</v>
+        <v>748</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>914</v>
+        <v>987</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>392</v>
+        <v>253</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>631</v>
+        <v>492</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>593</v>
+        <v>22</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>832</v>
+        <v>261</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>499</v>
+        <v>314</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>239</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>738</v>
+        <v>553</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>241</v>
@@ -55514,45 +55514,45 @@
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>139</v>
+        <v>460</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>378</v>
+        <v>699</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>63</v>
+        <v>161</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>302</v>
+        <v>400</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>15</v>
@@ -55560,19 +55560,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>472</v>
+        <v>277</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>711</v>
+        <v>516</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>235</v>
@@ -55583,22 +55583,22 @@
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>648</v>
+        <v>956</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>887</v>
+        <v>1195</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>15</v>
@@ -55606,22 +55606,22 @@
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>368</v>
+        <v>431</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>32</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>9</v>
@@ -55629,42 +55629,42 @@
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>977</v>
+        <v>386</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>221</v>
+        <v>94</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>1216</v>
+        <v>625</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>205</v>
+        <v>76</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>521</v>
+        <v>806</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>760</v>
+        <v>1045</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>232</v>
@@ -55675,19 +55675,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>839</v>
+        <v>414</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>239</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>191</v>
+        <v>101</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>1078</v>
+        <v>653</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>183</v>
+        <v>98</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>241</v>
@@ -55698,111 +55698,111 @@
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>963</v>
+        <v>492</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>218</v>
+        <v>117</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>1202</v>
+        <v>731</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>65</v>
+        <v>344</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>304</v>
+        <v>583</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>813</v>
+        <v>770</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1052</v>
+        <v>1009</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>15</v>
+        <v>309</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>254</v>
+        <v>548</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>157</v>
+        <v>662</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>396</v>
+        <v>901</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>235</v>
@@ -55813,19 +55813,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>280</v>
+        <v>370</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>232</v>
@@ -55836,137 +55836,137 @@
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>493</v>
+        <v>664</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>732</v>
+        <v>903</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>380</v>
+        <v>872</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>619</v>
+        <v>1111</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>76</v>
+        <v>183</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>427</v>
+        <v>339</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>764</v>
+        <v>373</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1003</v>
+        <v>612</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>217</v>
+        <v>88</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>456</v>
+        <v>327</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>792</v>
+        <v>459</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1031</v>
+        <v>698</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>9</v>
@@ -55974,22 +55974,22 @@
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>53</v>
+        <v>331</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>292</v>
+        <v>570</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>15</v>
@@ -55997,68 +55997,68 @@
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>879</v>
+        <v>215</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1118</v>
+        <v>454</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>183</v>
+        <v>54</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>338</v>
+        <v>467</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>577</v>
+        <v>706</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>749</v>
+        <v>122</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>172</v>
+        <v>37</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>988</v>
+        <v>361</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>9</v>
@@ -56066,19 +56066,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>720</v>
+        <v>615</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>242</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>959</v>
+        <v>854</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>244</v>
@@ -56089,42 +56089,42 @@
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>725</v>
+        <v>21</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>167</v>
+        <v>13</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>964</v>
+        <v>260</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>162</v>
+        <v>7</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>296</v>
+        <v>701</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>535</v>
+        <v>940</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>232</v>
@@ -56135,19 +56135,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>702</v>
+        <v>72</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>163</v>
+        <v>25</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>941</v>
+        <v>311</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>162</v>
+        <v>7</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>235</v>
@@ -56158,19 +56158,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>491</v>
+        <v>346</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>235</v>
@@ -56181,62 +56181,62 @@
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>727</v>
+        <v>271</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>966</v>
+        <v>510</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>462</v>
+        <v>861</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>701</v>
+        <v>1100</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>230</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>695</v>
+        <v>675</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>98</v>
@@ -56250,25 +56250,25 @@
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>997</v>
+        <v>103</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>225</v>
+        <v>33</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1236</v>
+        <v>342</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>205</v>
+        <v>32</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
